--- a/phong-tap-be/phong_tap-be/QuanLyPhongGym/src/main/resources/template/danh-sach-khach-hang-template.xlsx
+++ b/phong-tap-be/phong_tap-be/QuanLyPhongGym/src/main/resources/template/danh-sach-khach-hang-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Angular\DuAnDemo\quan-ly-phong-gym\phong-tap-be\phong_tap-be\QuanLyPhongGym\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054E1545-FA17-426A-BEF0-7E4DC5073C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06ADEA5C-BFFB-4C55-97EB-75722E222A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-19875" yWindow="9060" windowWidth="17280" windowHeight="8925" xr2:uid="{3EF13CE7-A9BD-40C4-8E04-D18B3A426551}"/>
+    <workbookView xWindow="-28920" yWindow="1995" windowWidth="29040" windowHeight="15720" xr2:uid="{3EF13CE7-A9BD-40C4-8E04-D18B3A426551}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,10 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
-  <si>
-    <t>Danh sách khách hàng</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>STT</t>
   </si>
@@ -66,8 +63,13 @@
     <t>Nội Dung</t>
   </si>
   <si>
-    <t xml:space="preserve">Loi: At least one recipient is required, but none were found._x000D_
-</t>
+    <t>Trạng thái</t>
+  </si>
+  <si>
+    <t>Tiêu đề</t>
+  </si>
+  <si>
+    <t>DANH SÁCH KHÁCH HÀNG</t>
   </si>
 </sst>
 </file>
@@ -153,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -164,6 +166,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -480,7 +485,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0D6FA1F-6AF0-4B5B-8059-D201A50AF440}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -488,14 +493,15 @@
     <col min="3" max="3" width="33" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.44140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="32" style="1" customWidth="1"/>
-    <col min="6" max="6" width="43.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="47" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="34.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="43.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="47" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -503,55 +509,58 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="42.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:E3" xr:uid="{B0D6FA1F-6AF0-4B5B-8059-D201A50AF440}"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/phong-tap-be/phong_tap-be/QuanLyPhongGym/src/main/resources/template/danh-sach-khach-hang-template.xlsx
+++ b/phong-tap-be/phong_tap-be/QuanLyPhongGym/src/main/resources/template/danh-sach-khach-hang-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Angular\DuAnDemo\quan-ly-phong-gym\phong-tap-be\phong_tap-be\QuanLyPhongGym\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06ADEA5C-BFFB-4C55-97EB-75722E222A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F184F66D-C537-4A7E-A25C-66477F7F959D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1995" windowWidth="29040" windowHeight="15720" xr2:uid="{3EF13CE7-A9BD-40C4-8E04-D18B3A426551}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EF13CE7-A9BD-40C4-8E04-D18B3A426551}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -164,11 +164,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,32 +486,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0D6FA1F-6AF0-4B5B-8059-D201A50AF440}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="26.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="1"/>
+    <col min="2" max="2" width="26.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="33" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="32" style="1" customWidth="1"/>
-    <col min="6" max="6" width="34.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="43.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="34.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="43.28515625" style="1" customWidth="1"/>
     <col min="8" max="8" width="47" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="9" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
-    <row r="2" spans="1:8" ht="42.6" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -537,7 +537,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -553,8 +553,8 @@
       <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
       <c r="H3" s="2"/>
     </row>
   </sheetData>
